--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Id</t>
   </si>
@@ -45,6 +45,18 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>90000000000</t>
+  </si>
+  <si>
+    <t>270000000000</t>
+  </si>
+  <si>
+    <t>810000000000</t>
   </si>
 </sst>
 </file>
@@ -688,6 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1036,20 +1049,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="C3:F37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" ht="13.5" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1088,7 +1101,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="3:6">
@@ -1110,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D34" si="0">E6+1</f>
+        <f t="shared" ref="D7:D37" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1372,7 +1385,7 @@
         <v>150000</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" ref="F24:F34" si="1">F23*3</f>
+        <f t="shared" ref="F24:F37" si="1">F23*3</f>
         <v>600000</v>
       </c>
     </row>
@@ -1477,7 +1490,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1">
-        <f>E30+1</f>
+        <f t="shared" si="0"/>
         <v>210001</v>
       </c>
       <c r="E31" s="1">
@@ -1532,8 +1545,53 @@
         <v>260000</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="1"/>
+        <f>F33*3</f>
         <v>35429400000</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>260001</v>
+      </c>
+      <c r="E35" s="1">
+        <v>270000</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>270001</v>
+      </c>
+      <c r="E36" s="1">
+        <v>280000</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>280001</v>
+      </c>
+      <c r="E37" s="1">
+        <v>290000</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -57,6 +57,21 @@
   </si>
   <si>
     <t>810000000000</t>
+  </si>
+  <si>
+    <t>2430000000000</t>
+  </si>
+  <si>
+    <t>7200000000000</t>
+  </si>
+  <si>
+    <t>21600000000000</t>
+  </si>
+  <si>
+    <t>64800000000000</t>
+  </si>
+  <si>
+    <t>195000000000000</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F37"/>
+  <dimension ref="C3:F42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
@@ -1123,7 +1138,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D37" si="0">E6+1</f>
+        <f t="shared" ref="D7:D42" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1592,6 +1607,81 @@
       </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>290001</v>
+      </c>
+      <c r="E38" s="1">
+        <v>300000</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>300001</v>
+      </c>
+      <c r="E39" s="1">
+        <v>310000</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>310001</v>
+      </c>
+      <c r="E40" s="1">
+        <v>320000</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>320001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>330000</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="0"/>
+        <v>330001</v>
+      </c>
+      <c r="E42" s="1">
+        <v>340000</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -1065,19 +1065,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:F42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.50442477876106" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12389380530973" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1858407079646" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2566371681416" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:6">
+    <row r="3" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:6">
+    <row r="4" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:6">
+    <row r="5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>1000</v>
       </c>
       <c r="F9" s="1">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="3:6">
@@ -1190,7 +1190,7 @@
         <v>2000</v>
       </c>
       <c r="F10" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="3:6">
@@ -1205,7 +1205,7 @@
         <v>5000</v>
       </c>
       <c r="F11" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="3:6">
@@ -1220,7 +1220,7 @@
         <v>10000</v>
       </c>
       <c r="F12" s="1">
-        <v>2100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="3:6">
@@ -1235,7 +1235,7 @@
         <v>20000</v>
       </c>
       <c r="F13" s="1">
-        <v>2800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="3:6">
@@ -1250,7 +1250,7 @@
         <v>30000</v>
       </c>
       <c r="F14" s="1">
-        <v>2100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="3:6">
@@ -1265,7 +1265,7 @@
         <v>40000</v>
       </c>
       <c r="F15" s="1">
-        <v>4500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="3:6">
@@ -1280,7 +1280,7 @@
         <v>50000</v>
       </c>
       <c r="F16" s="1">
-        <v>8000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="17" spans="3:6">
@@ -1295,7 +1295,7 @@
         <v>60000</v>
       </c>
       <c r="F17" s="1">
-        <v>13000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="18" spans="3:6">
@@ -1310,7 +1310,7 @@
         <v>70000</v>
       </c>
       <c r="F18" s="1">
-        <v>18000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="19" spans="3:6">
@@ -1325,7 +1325,7 @@
         <v>80000</v>
       </c>
       <c r="F19" s="1">
-        <v>23000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="20" spans="3:6">
@@ -1340,7 +1340,7 @@
         <v>100000</v>
       </c>
       <c r="F20" s="1">
-        <v>28000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="21" spans="3:6">
@@ -1355,7 +1355,7 @@
         <v>120000</v>
       </c>
       <c r="F21" s="1">
-        <v>33000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="22" spans="3:6">
@@ -1560,7 +1560,7 @@
         <v>260000</v>
       </c>
       <c r="F34" s="1">
-        <f>F33*3</f>
+        <f t="shared" si="1"/>
         <v>35429400000</v>
       </c>
     </row>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -1065,19 +1065,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:F42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.50442477876106" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.12389380530973" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.1858407079646" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.2566371681416" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" ht="13.5" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>1000</v>
       </c>
       <c r="F9" s="1">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="3:6">
@@ -1190,7 +1190,7 @@
         <v>2000</v>
       </c>
       <c r="F10" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="3:6">
@@ -1205,7 +1205,7 @@
         <v>5000</v>
       </c>
       <c r="F11" s="1">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="3:6">
@@ -1220,7 +1220,7 @@
         <v>10000</v>
       </c>
       <c r="F12" s="1">
-        <v>1000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="13" spans="3:6">
@@ -1235,7 +1235,7 @@
         <v>20000</v>
       </c>
       <c r="F13" s="1">
-        <v>1000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="3:6">
@@ -1250,7 +1250,7 @@
         <v>30000</v>
       </c>
       <c r="F14" s="1">
-        <v>1000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="15" spans="3:6">
@@ -1265,7 +1265,7 @@
         <v>40000</v>
       </c>
       <c r="F15" s="1">
-        <v>2000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="16" spans="3:6">
@@ -1280,7 +1280,7 @@
         <v>50000</v>
       </c>
       <c r="F16" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="17" spans="3:6">
@@ -1295,7 +1295,7 @@
         <v>60000</v>
       </c>
       <c r="F17" s="1">
-        <v>7000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="18" spans="3:6">
@@ -1310,7 +1310,7 @@
         <v>70000</v>
       </c>
       <c r="F18" s="1">
-        <v>8000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="19" spans="3:6">
@@ -1325,7 +1325,7 @@
         <v>80000</v>
       </c>
       <c r="F19" s="1">
-        <v>11000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="20" spans="3:6">
@@ -1340,7 +1340,7 @@
         <v>100000</v>
       </c>
       <c r="F20" s="1">
-        <v>14000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="21" spans="3:6">
@@ -1355,7 +1355,7 @@
         <v>120000</v>
       </c>
       <c r="F21" s="1">
-        <v>17000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="22" spans="3:6">
@@ -1560,7 +1560,7 @@
         <v>260000</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="1"/>
+        <f>F33*3</f>
         <v>35429400000</v>
       </c>
     </row>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>195000000000000</t>
+  </si>
+  <si>
+    <t>600000000000000</t>
+  </si>
+  <si>
+    <t>1800000000000000</t>
+  </si>
+  <si>
+    <t>5400000000000000</t>
+  </si>
+  <si>
+    <t>16000000000000000</t>
+  </si>
+  <si>
+    <t>48000000000000000</t>
+  </si>
+  <si>
+    <t>15000000000000000</t>
   </si>
 </sst>
 </file>
@@ -1064,20 +1082,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
+  <dimension ref="C3:F48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.50442477876106" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12389380530973" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1858407079646" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2566371681416" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:6">
+    <row r="3" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:6">
+    <row r="4" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:6">
+    <row r="5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1138,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D42" si="0">E6+1</f>
+        <f t="shared" ref="D7:D48" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1560,7 +1578,7 @@
         <v>260000</v>
       </c>
       <c r="F34" s="1">
-        <f>F33*3</f>
+        <f t="shared" si="1"/>
         <v>35429400000</v>
       </c>
     </row>
@@ -1682,6 +1700,96 @@
       </c>
       <c r="F42" s="3" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="0"/>
+        <v>340001</v>
+      </c>
+      <c r="E43" s="1">
+        <v>350000</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="0"/>
+        <v>350001</v>
+      </c>
+      <c r="E44" s="1">
+        <v>360000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="0"/>
+        <v>360001</v>
+      </c>
+      <c r="E45" s="1">
+        <v>370000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="0"/>
+        <v>370001</v>
+      </c>
+      <c r="E46" s="1">
+        <v>380000</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="0"/>
+        <v>380001</v>
+      </c>
+      <c r="E47" s="1">
+        <v>390000</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="0"/>
+        <v>390001</v>
+      </c>
+      <c r="E48" s="1">
+        <v>400000</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -89,7 +89,16 @@
     <t>48000000000000000</t>
   </si>
   <si>
-    <t>15000000000000000</t>
+    <t>150000000000000000</t>
+  </si>
+  <si>
+    <t>300000000000000000</t>
+  </si>
+  <si>
+    <t>600000000000000000</t>
+  </si>
+  <si>
+    <t>900000000000000000</t>
   </si>
 </sst>
 </file>
@@ -1082,20 +1091,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="5"/>
+  <dimension ref="C3:F51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.50442477876106" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.12389380530973" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.1858407079646" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.2566371681416" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" ht="13.5" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1123,7 +1132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1156,7 +1165,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D48" si="0">E6+1</f>
+        <f t="shared" ref="D7:D51" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1790,6 +1799,51 @@
       </c>
       <c r="F48" s="3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="3:6">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="0"/>
+        <v>400001</v>
+      </c>
+      <c r="E49" s="1">
+        <v>410000</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="3:6">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <f t="shared" si="0"/>
+        <v>410001</v>
+      </c>
+      <c r="E50" s="1">
+        <v>420000</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="3:6">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1">
+        <f t="shared" si="0"/>
+        <v>420001</v>
+      </c>
+      <c r="E51" s="1">
+        <v>430000</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>long</t>
   </si>
   <si>
-    <t>double</t>
+    <t>string</t>
   </si>
   <si>
     <t>90000000000</t>
@@ -98,7 +98,46 @@
     <t>600000000000000000</t>
   </si>
   <si>
-    <t>900000000000000000</t>
+    <t>1000000000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000</t>
+  </si>
+  <si>
+    <t>16000000000000000000</t>
+  </si>
+  <si>
+    <t>30000000000000000000</t>
+  </si>
+  <si>
+    <t>60000000000000000000</t>
+  </si>
+  <si>
+    <t>120000000000000000000</t>
+  </si>
+  <si>
+    <t>240000000000000000000</t>
+  </si>
+  <si>
+    <t>480000000000000000000</t>
+  </si>
+  <si>
+    <t>1000000000000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F51"/>
+  <dimension ref="C3:F64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
@@ -1165,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D51" si="0">E6+1</f>
+        <f t="shared" ref="D7:D64" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1844,6 +1883,201 @@
       </c>
       <c r="F51" s="3" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="3:6">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <f t="shared" si="0"/>
+        <v>430001</v>
+      </c>
+      <c r="E52" s="1">
+        <v>440000</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <f t="shared" si="0"/>
+        <v>440001</v>
+      </c>
+      <c r="E53" s="1">
+        <v>450000</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" si="0"/>
+        <v>450001</v>
+      </c>
+      <c r="E54" s="1">
+        <v>460000</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <f t="shared" si="0"/>
+        <v>460001</v>
+      </c>
+      <c r="E55" s="1">
+        <v>470000</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="3:6">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" si="0"/>
+        <v>470001</v>
+      </c>
+      <c r="E56" s="1">
+        <v>480000</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="3:6">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="0"/>
+        <v>480001</v>
+      </c>
+      <c r="E57" s="1">
+        <v>490000</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1">
+        <f t="shared" si="0"/>
+        <v>490001</v>
+      </c>
+      <c r="E58" s="1">
+        <v>500000</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="3:6">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1">
+        <f t="shared" si="0"/>
+        <v>500001</v>
+      </c>
+      <c r="E59" s="1">
+        <v>510000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <f t="shared" si="0"/>
+        <v>510001</v>
+      </c>
+      <c r="E60" s="1">
+        <v>520000</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="3:6">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="1">
+        <f t="shared" si="0"/>
+        <v>520001</v>
+      </c>
+      <c r="E61" s="1">
+        <v>530000</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="3:6">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1">
+        <f t="shared" si="0"/>
+        <v>530001</v>
+      </c>
+      <c r="E62" s="1">
+        <v>540000</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="3:6">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1">
+        <f t="shared" si="0"/>
+        <v>540001</v>
+      </c>
+      <c r="E63" s="1">
+        <v>550000</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="3:6">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1">
+        <f t="shared" si="0"/>
+        <v>550001</v>
+      </c>
+      <c r="E64" s="1">
+        <v>560000</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
